--- a/output_data/charts/0500000US39127.xlsx
+++ b/output_data/charts/0500000US39127.xlsx
@@ -167,10 +167,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -212,16 +212,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$15</c:f>
+              <c:f>Sheet1!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.1026722535172184</c:v>
                 </c:pt>
@@ -253,16 +256,19 @@
                   <c:v>0.1937608990505716</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.1974834960221181</c:v>
+                  <c:v>0.1974333662388943</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.214301827205053</c:v>
+                  <c:v>0.2142172614014319</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.22271714922049</c:v>
+                  <c:v>0.225460079474678</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.2362802734100307</c:v>
+                  <c:v>0.2361075976051943</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2326102796928423</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -292,10 +298,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -337,16 +343,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$15</c:f>
+              <c:f>Sheet1!$C$2:$C$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2608430224491495</c:v>
                 </c:pt>
@@ -378,16 +387,19 @@
                   <c:v>0.4677941705649514</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5303842464594031</c:v>
+                  <c:v>0.5302496121844592</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.5611324159711256</c:v>
+                  <c:v>0.5609109870905914</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.6455978122973697</c:v>
+                  <c:v>0.6425612265028324</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6553964726730612</c:v>
+                  <c:v>0.6774039407482362</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.7987220447284344</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,10 +429,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -462,16 +474,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$15</c:f>
+              <c:f>Sheet1!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.5411105252934484</c:v>
                 </c:pt>
@@ -503,16 +518,19 @@
                   <c:v>0.8913001356326293</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.7052982000789935</c:v>
+                  <c:v>0.7051191651389085</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8205504173246109</c:v>
+                  <c:v>0.8174079711370427</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8767725747793973</c:v>
+                  <c:v>0.8736578079643773</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.9788754184129842</c:v>
+                  <c:v>0.9894032661551002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.039739924892102</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -542,10 +560,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -587,16 +605,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$15</c:f>
+              <c:f>Sheet1!$E$2:$E$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.2608430224491495</c:v>
                 </c:pt>
@@ -628,16 +649,19 @@
                   <c:v>0.442882054972735</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.4570332336511878</c:v>
+                  <c:v>0.4597376956705684</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.4680803067899842</c:v>
+                  <c:v>0.4707142454478832</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4679879338050802</c:v>
+                  <c:v>0.4706479159033904</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4725605468200614</c:v>
+                  <c:v>0.4750259999437839</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.4680230928759598</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -667,10 +691,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -712,16 +736,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$15</c:f>
+              <c:f>Sheet1!$F$2:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.204317784499265</c:v>
                 </c:pt>
@@ -753,16 +780,19 @@
                   <c:v>1.411686550225593</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.461377870563674</c:v>
+                  <c:v>1.461006910167818</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.545228964583803</c:v>
+                  <c:v>1.541800552455043</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.60412731527163</c:v>
+                  <c:v>1.606403066257081</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.62583330989283</c:v>
+                  <c:v>1.613401916968828</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.661902359733199</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,10 +822,10 @@
           </c:spPr>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$15</c:f>
+              <c:f>Sheet1!$A$2:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2010</c:v>
                 </c:pt>
@@ -837,16 +867,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$2:$G$15</c:f>
+              <c:f>Sheet1!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>97.63021339179177</c:v>
                 </c:pt>
@@ -878,16 +911,19 @@
                   <c:v>96.59257618955351</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>96.64842295322462</c:v>
+                  <c:v>96.64645325059935</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>96.39070606812543</c:v>
+                  <c:v>96.39494898246801</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>96.18279721462604</c:v>
+                  <c:v>96.18126990389764</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>96.03105397879104</c:v>
+                  <c:v>96.00865727857885</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>95.79900229807747</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,13 +1042,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1428750</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1320,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.7109375" style="1" customWidth="1"/>
@@ -1590,22 +1626,22 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2">
-        <v>0.1974834960221181</v>
+        <v>0.1974333662388943</v>
       </c>
       <c r="C12" s="2">
-        <v>0.5303842464594031</v>
+        <v>0.5302496121844592</v>
       </c>
       <c r="D12" s="2">
-        <v>0.7052982000789935</v>
+        <v>0.7051191651389085</v>
       </c>
       <c r="E12" s="2">
-        <v>0.4570332336511878</v>
+        <v>0.4597376956705684</v>
       </c>
       <c r="F12" s="2">
-        <v>1.461377870563674</v>
+        <v>1.461006910167818</v>
       </c>
       <c r="G12" s="2">
-        <v>96.64842295322462</v>
+        <v>96.64645325059935</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1613,22 +1649,22 @@
         <v>2021</v>
       </c>
       <c r="B13" s="2">
-        <v>0.214301827205053</v>
+        <v>0.2142172614014319</v>
       </c>
       <c r="C13" s="2">
-        <v>0.5611324159711256</v>
+        <v>0.5609109870905914</v>
       </c>
       <c r="D13" s="2">
-        <v>0.8205504173246109</v>
+        <v>0.8174079711370427</v>
       </c>
       <c r="E13" s="2">
-        <v>0.4680803067899842</v>
+        <v>0.4707142454478832</v>
       </c>
       <c r="F13" s="2">
-        <v>1.545228964583803</v>
+        <v>1.541800552455043</v>
       </c>
       <c r="G13" s="2">
-        <v>96.39070606812543</v>
+        <v>96.39494898246801</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1636,22 +1672,22 @@
         <v>2022</v>
       </c>
       <c r="B14" s="2">
-        <v>0.22271714922049</v>
+        <v>0.225460079474678</v>
       </c>
       <c r="C14" s="2">
-        <v>0.6455978122973697</v>
+        <v>0.6425612265028324</v>
       </c>
       <c r="D14" s="2">
-        <v>0.8767725747793973</v>
+        <v>0.8736578079643773</v>
       </c>
       <c r="E14" s="2">
-        <v>0.4679879338050802</v>
+        <v>0.4706479159033904</v>
       </c>
       <c r="F14" s="2">
-        <v>1.60412731527163</v>
+        <v>1.606403066257081</v>
       </c>
       <c r="G14" s="2">
-        <v>96.18279721462604</v>
+        <v>96.18126990389764</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1659,22 +1695,45 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>0.2362802734100307</v>
+        <v>0.2361075976051943</v>
       </c>
       <c r="C15" s="2">
-        <v>0.6553964726730612</v>
+        <v>0.6774039407482362</v>
       </c>
       <c r="D15" s="2">
-        <v>0.9788754184129842</v>
+        <v>0.9894032661551002</v>
       </c>
       <c r="E15" s="2">
-        <v>0.4725605468200614</v>
+        <v>0.4750259999437839</v>
       </c>
       <c r="F15" s="2">
-        <v>1.62583330989283</v>
+        <v>1.613401916968828</v>
       </c>
       <c r="G15" s="2">
-        <v>96.03105397879104</v>
+        <v>96.00865727857885</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.2326102796928423</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.7987220447284344</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1.039739924892102</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.4680230928759598</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1.661902359733199</v>
+      </c>
+      <c r="G16" s="2">
+        <v>95.79900229807747</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/0500000US39127.xlsx
+++ b/output_data/charts/0500000US39127.xlsx
@@ -229,10 +229,10 @@
                   <c:v>0.1026722535172184</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1076485688260785</c:v>
+                  <c:v>0.1076396555531022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1389545062946392</c:v>
+                  <c:v>0.1389506447309916</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.1388888888888889</c:v>
@@ -241,19 +241,19 @@
                   <c:v>0.1419584701887213</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.158465387823186</c:v>
+                  <c:v>0.1584786053882726</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.1638206302929335</c:v>
+                  <c:v>0.1638979943330185</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.1612230715774844</c:v>
+                  <c:v>0.1584565773379295</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.1664539754757809</c:v>
+                  <c:v>0.1609367629512473</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1937608990505716</c:v>
+                  <c:v>0.1881884098079371</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.1974333662388943</c:v>
@@ -357,34 +357,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2608430224491495</c:v>
+                  <c:v>0.2691677997613564</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3119048276242789</c:v>
+                  <c:v>0.3229189666593067</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3501653558624906</c:v>
+                  <c:v>0.3696087149844375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3444444444444444</c:v>
+                  <c:v>0.3666666666666666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3674219228413962</c:v>
+                  <c:v>0.3980404164115126</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.369752571587434</c:v>
+                  <c:v>0.4059276559068035</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3665139525197835</c:v>
+                  <c:v>0.4000222234568587</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4113968033356497</c:v>
+                  <c:v>0.4503502724341154</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.4716195971813794</c:v>
+                  <c:v>0.5105580066039568</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.4677941705649514</c:v>
+                  <c:v>0.5064482205125367</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.5302496121844592</c:v>
@@ -491,31 +491,31 @@
                   <c:v>0.5411105252934484</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.6182892158215795</c:v>
+                  <c:v>0.620998012806359</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.6503070894589111</c:v>
+                  <c:v>0.6558470431302801</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.6833333333333333</c:v>
+                  <c:v>0.6888888888888889</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7682458386683738</c:v>
+                  <c:v>0.7765963369147693</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.8006672226855712</c:v>
+                  <c:v>0.8118553118136069</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.8357628765792031</c:v>
+                  <c:v>0.8444913606311462</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.8978457261987491</c:v>
+                  <c:v>0.9034804848215278</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.8711091383232537</c:v>
+                  <c:v>0.8574044784816449</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.8913001356326293</c:v>
+                  <c:v>0.8745226102839432</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.7051191651389085</c:v>
@@ -622,31 +622,31 @@
                   <c:v>0.2608430224491495</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.270501531921941</c:v>
+                  <c:v>0.273239125634798</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.280688102715171</c:v>
+                  <c:v>0.2834593152512228</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3361111111111111</c:v>
+                  <c:v>0.3416666666666667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3340199298558147</c:v>
+                  <c:v>0.3395869286867449</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3391715318320823</c:v>
+                  <c:v>0.3447604748797509</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.3720671942246286</c:v>
+                  <c:v>0.3805766987054836</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.3835997220291869</c:v>
+                  <c:v>0.3919715334148782</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3939410752926815</c:v>
+                  <c:v>0.4051166791531396</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.442882054972735</c:v>
+                  <c:v>0.4510986882160846</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0.4597376956705684</c:v>
@@ -750,34 +750,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.204317784499265</c:v>
+                  <c:v>1.209867636040736</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.236578431643159</c:v>
+                  <c:v>1.247516007948775</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.214462385015146</c:v>
+                  <c:v>1.228323699421965</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.197222222222222</c:v>
+                  <c:v>1.211111111111111</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.311028224684073</c:v>
+                  <c:v>1.322162222345933</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.359466221851543</c:v>
+                  <c:v>1.367920593877721</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.391087047063724</c:v>
+                  <c:v>1.408411578421023</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.392633773453787</c:v>
+                  <c:v>1.406649616368286</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.389890695222771</c:v>
+                  <c:v>1.404034518160881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.411686550225593</c:v>
+                  <c:v>1.433552886478109</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.461006910167818</c:v>
@@ -881,34 +881,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>97.63021339179177</c:v>
+                  <c:v>97.6163387629381</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>97.45507742416297</c:v>
+                  <c:v>97.42768823139765</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>97.36542256065364</c:v>
+                  <c:v>97.3238105824811</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>97.3</c:v>
+                  <c:v>97.25277777777778</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>97.07732561376162</c:v>
+                  <c:v>97.02165562545233</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>96.97247706422019</c:v>
+                  <c:v>96.91105735813385</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>96.87074829931973</c:v>
+                  <c:v>96.80260014445247</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>96.75330090340513</c:v>
+                  <c:v>96.68909151562326</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>96.70698551850413</c:v>
+                  <c:v>96.66194955464913</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>96.59257618955351</c:v>
+                  <c:v>96.54618918470139</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>96.64645325059935</c:v>
@@ -1399,7 +1399,7 @@
         <v>0.1026722535172184</v>
       </c>
       <c r="C2" s="2">
-        <v>0.2608430224491495</v>
+        <v>0.2691677997613564</v>
       </c>
       <c r="D2" s="2">
         <v>0.5411105252934484</v>
@@ -1408,10 +1408,10 @@
         <v>0.2608430224491495</v>
       </c>
       <c r="F2" s="2">
-        <v>1.204317784499265</v>
+        <v>1.209867636040736</v>
       </c>
       <c r="G2" s="2">
-        <v>97.63021339179177</v>
+        <v>97.6163387629381</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1419,22 +1419,22 @@
         <v>2011</v>
       </c>
       <c r="B3" s="2">
-        <v>0.1076485688260785</v>
+        <v>0.1076396555531022</v>
       </c>
       <c r="C3" s="2">
-        <v>0.3119048276242789</v>
+        <v>0.3229189666593067</v>
       </c>
       <c r="D3" s="2">
-        <v>0.6182892158215795</v>
+        <v>0.620998012806359</v>
       </c>
       <c r="E3" s="2">
-        <v>0.270501531921941</v>
+        <v>0.273239125634798</v>
       </c>
       <c r="F3" s="2">
-        <v>1.236578431643159</v>
+        <v>1.247516007948775</v>
       </c>
       <c r="G3" s="2">
-        <v>97.45507742416297</v>
+        <v>97.42768823139765</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1442,22 +1442,22 @@
         <v>2012</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1389545062946392</v>
+        <v>0.1389506447309916</v>
       </c>
       <c r="C4" s="2">
-        <v>0.3501653558624906</v>
+        <v>0.3696087149844375</v>
       </c>
       <c r="D4" s="2">
-        <v>0.6503070894589111</v>
+        <v>0.6558470431302801</v>
       </c>
       <c r="E4" s="2">
-        <v>0.280688102715171</v>
+        <v>0.2834593152512228</v>
       </c>
       <c r="F4" s="2">
-        <v>1.214462385015146</v>
+        <v>1.228323699421965</v>
       </c>
       <c r="G4" s="2">
-        <v>97.36542256065364</v>
+        <v>97.3238105824811</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1468,19 +1468,19 @@
         <v>0.1388888888888889</v>
       </c>
       <c r="C5" s="2">
-        <v>0.3444444444444444</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="D5" s="2">
-        <v>0.6833333333333333</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="E5" s="2">
-        <v>0.3361111111111111</v>
+        <v>0.3416666666666667</v>
       </c>
       <c r="F5" s="2">
-        <v>1.197222222222222</v>
+        <v>1.211111111111111</v>
       </c>
       <c r="G5" s="2">
-        <v>97.3</v>
+        <v>97.25277777777778</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1491,19 +1491,19 @@
         <v>0.1419584701887213</v>
       </c>
       <c r="C6" s="2">
-        <v>0.3674219228413962</v>
+        <v>0.3980404164115126</v>
       </c>
       <c r="D6" s="2">
-        <v>0.7682458386683738</v>
+        <v>0.7765963369147693</v>
       </c>
       <c r="E6" s="2">
-        <v>0.3340199298558147</v>
+        <v>0.3395869286867449</v>
       </c>
       <c r="F6" s="2">
-        <v>1.311028224684073</v>
+        <v>1.322162222345933</v>
       </c>
       <c r="G6" s="2">
-        <v>97.07732561376162</v>
+        <v>97.02165562545233</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1511,22 +1511,22 @@
         <v>2015</v>
       </c>
       <c r="B7" s="2">
-        <v>0.158465387823186</v>
+        <v>0.1584786053882726</v>
       </c>
       <c r="C7" s="2">
-        <v>0.369752571587434</v>
+        <v>0.4059276559068035</v>
       </c>
       <c r="D7" s="2">
-        <v>0.8006672226855712</v>
+        <v>0.8118553118136069</v>
       </c>
       <c r="E7" s="2">
-        <v>0.3391715318320823</v>
+        <v>0.3447604748797509</v>
       </c>
       <c r="F7" s="2">
-        <v>1.359466221851543</v>
+        <v>1.367920593877721</v>
       </c>
       <c r="G7" s="2">
-        <v>96.97247706422019</v>
+        <v>96.91105735813385</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1534,22 +1534,22 @@
         <v>2016</v>
       </c>
       <c r="B8" s="2">
-        <v>0.1638206302929335</v>
+        <v>0.1638979943330185</v>
       </c>
       <c r="C8" s="2">
-        <v>0.3665139525197835</v>
+        <v>0.4000222234568587</v>
       </c>
       <c r="D8" s="2">
-        <v>0.8357628765792031</v>
+        <v>0.8444913606311462</v>
       </c>
       <c r="E8" s="2">
-        <v>0.3720671942246286</v>
+        <v>0.3805766987054836</v>
       </c>
       <c r="F8" s="2">
-        <v>1.391087047063724</v>
+        <v>1.408411578421023</v>
       </c>
       <c r="G8" s="2">
-        <v>96.87074829931973</v>
+        <v>96.80260014445247</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1557,22 +1557,22 @@
         <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>0.1612230715774844</v>
+        <v>0.1584565773379295</v>
       </c>
       <c r="C9" s="2">
-        <v>0.4113968033356497</v>
+        <v>0.4503502724341154</v>
       </c>
       <c r="D9" s="2">
-        <v>0.8978457261987491</v>
+        <v>0.9034804848215278</v>
       </c>
       <c r="E9" s="2">
-        <v>0.3835997220291869</v>
+        <v>0.3919715334148782</v>
       </c>
       <c r="F9" s="2">
-        <v>1.392633773453787</v>
+        <v>1.406649616368286</v>
       </c>
       <c r="G9" s="2">
-        <v>96.75330090340513</v>
+        <v>96.68909151562326</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1580,22 +1580,22 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2">
-        <v>0.1664539754757809</v>
+        <v>0.1609367629512473</v>
       </c>
       <c r="C10" s="2">
-        <v>0.4716195971813794</v>
+        <v>0.5105580066039568</v>
       </c>
       <c r="D10" s="2">
-        <v>0.8711091383232537</v>
+        <v>0.8574044784816449</v>
       </c>
       <c r="E10" s="2">
-        <v>0.3939410752926815</v>
+        <v>0.4051166791531396</v>
       </c>
       <c r="F10" s="2">
-        <v>1.389890695222771</v>
+        <v>1.404034518160881</v>
       </c>
       <c r="G10" s="2">
-        <v>96.70698551850413</v>
+        <v>96.66194955464913</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1603,22 +1603,22 @@
         <v>2019</v>
       </c>
       <c r="B11" s="2">
-        <v>0.1937608990505716</v>
+        <v>0.1881884098079371</v>
       </c>
       <c r="C11" s="2">
-        <v>0.4677941705649514</v>
+        <v>0.5064482205125367</v>
       </c>
       <c r="D11" s="2">
-        <v>0.8913001356326293</v>
+        <v>0.8745226102839432</v>
       </c>
       <c r="E11" s="2">
-        <v>0.442882054972735</v>
+        <v>0.4510986882160846</v>
       </c>
       <c r="F11" s="2">
-        <v>1.411686550225593</v>
+        <v>1.433552886478109</v>
       </c>
       <c r="G11" s="2">
-        <v>96.59257618955351</v>
+        <v>96.54618918470139</v>
       </c>
     </row>
     <row r="12" spans="1:7">
